--- a/短线标的_20260615.xlsx
+++ b/短线标的_20260615.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +33,34 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00BF8F00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -46,7 +68,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +78,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,18 +127,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -469,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -540,7 +604,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>换手率</t>
+          <t>成交额(万)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -584,57 +648,633 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 0 只标的</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>创业板</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>847708.0468670001</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>动量延续: 涨3.69%振幅4.95%成交额84.77亿</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sz300059.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>北方稀土</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>753764.12</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>动量延续: 涨4.02%振幅6.71%成交额75.38亿</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600111.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>600030</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>非银金融</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>非银金融</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>702763.8104</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>动量延续: 涨3.06%振幅4.47%成交额70.28亿</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600030.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>有色金属</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>有色金属</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1471798.3134</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>动量延续: 涨6.44%振幅7.14%成交额147.18亿</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh601899.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>天齐锂业</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>002466</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>614089.39855</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>超跌反弹: 涨2.46%振幅5.36%成交额61.41亿</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sz002466.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>天赐材料</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>002709</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>基础化工</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>基础化工</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>607991.6284789999</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>超跌反弹: 涨2.43%振幅5.63%成交额60.80亿</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sz002709.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>603259</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>601841.2066</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>超跌反弹: 涨2.72%振幅4.96%成交额60.18亿</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>93.73</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh603259.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>新奥股份</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>600803</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>22262.5608</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>资金埋伏: 涨0.55%振幅4.22%成交额2.23亿</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600803.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 8 只标的</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>策略说明：</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35 — 仓位12-15%</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/政策 — 仓位5-12%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向连续净买+主力流入&gt;3000万 — 仓位3-8%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>E 回调企稳突破：回调MA20±3%+缩量+站回MA5 — 仓位8-15%</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -642,14 +1282,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A7:R7"/>
-    <mergeCell ref="A10:R10"/>
-    <mergeCell ref="A5:R5"/>
-    <mergeCell ref="A9:R9"/>
-    <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A6:R6"/>
-    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="A16:R16"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A13:R13"/>
+    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A17:R17"/>
+    <mergeCell ref="A12:R12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
